--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,11 +571,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -623,11 +619,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -680,11 +672,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -735,11 +723,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -892,11 +876,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18/27</t>
@@ -947,11 +927,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2349,11 +2325,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -2411,11 +2383,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -2473,11 +2441,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -2535,11 +2499,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -2683,11 +2643,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>18/27</t>
@@ -2730,11 +2686,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -3637,11 +3589,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3684,11 +3632,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3731,11 +3675,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>17/31</t>
@@ -3778,11 +3718,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>15/31</t>
@@ -3911,11 +3847,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3958,11 +3890,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>13/31</t>
@@ -4865,11 +4793,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -4912,11 +4836,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -4959,11 +4879,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>17/31</t>
@@ -5006,11 +4922,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>15/31</t>
@@ -5139,11 +5051,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -5186,11 +5094,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>13/31</t>
@@ -6093,11 +5997,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>7/19</t>
@@ -6140,11 +6040,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>6/19</t>
@@ -6187,11 +6083,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>3/19</t>
@@ -6234,11 +6126,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>7/19</t>
@@ -6367,11 +6255,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>11/19</t>
@@ -6414,11 +6298,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>10/19</t>
@@ -6676,11 +6556,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>1/19</t>
@@ -7325,11 +7201,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>7/19</t>
@@ -7372,11 +7244,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>6/19</t>
@@ -7419,11 +7287,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
           <t>3/19</t>
@@ -7466,11 +7330,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>7/19</t>
@@ -7599,11 +7459,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>11/19</t>
@@ -7646,11 +7502,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>10/19</t>
@@ -7908,11 +7760,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>1/19</t>
@@ -8557,11 +8405,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -8604,11 +8448,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>16/21</t>
@@ -8651,11 +8491,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -8698,11 +8534,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -8831,11 +8663,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
           <t>13/21</t>
@@ -8878,11 +8706,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -9785,11 +9609,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -9832,11 +9652,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
           <t>16/21</t>
@@ -9879,11 +9695,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -9926,11 +9738,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G201" s="2" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -10059,11 +9867,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G204" s="2" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr">
         <is>
           <t>13/21</t>
@@ -10106,11 +9910,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G205" s="2" t="inlineStr"/>
       <c r="H205" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -11013,11 +10813,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G226" s="2" t="inlineStr"/>
       <c r="H226" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -11060,11 +10856,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -11107,11 +10899,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -11154,11 +10942,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -11287,11 +11071,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G232" s="2" t="inlineStr"/>
       <c r="H232" s="2" t="inlineStr">
         <is>
           <t>24/31</t>
@@ -11334,11 +11114,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G233" s="2" t="inlineStr"/>
       <c r="H233" s="2" t="inlineStr">
         <is>
           <t>31/31</t>
@@ -12241,11 +12017,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G254" s="2" t="inlineStr"/>
       <c r="H254" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -12288,11 +12060,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G255" s="2" t="inlineStr"/>
       <c r="H255" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -12335,11 +12103,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -12382,11 +12146,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G257" s="2" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -12515,11 +12275,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G260" s="2" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr">
         <is>
           <t>24/31</t>
@@ -12562,11 +12318,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G261" s="2" t="inlineStr"/>
       <c r="H261" s="2" t="inlineStr">
         <is>
           <t>31/31</t>
@@ -13469,11 +13221,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G282" s="2" t="inlineStr"/>
       <c r="H282" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -13516,11 +13264,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G283" s="2" t="inlineStr"/>
       <c r="H283" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -13563,11 +13307,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G284" s="2" t="inlineStr"/>
       <c r="H284" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -13610,11 +13350,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G285" s="2" t="inlineStr"/>
       <c r="H285" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -13743,11 +13479,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G288" s="2" t="inlineStr"/>
       <c r="H288" s="2" t="inlineStr">
         <is>
           <t>20/28</t>
@@ -13790,11 +13522,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G289" s="2" t="inlineStr"/>
       <c r="H289" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -14697,11 +14425,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G310" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G310" s="2" t="inlineStr"/>
       <c r="H310" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -14744,11 +14468,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G311" s="2" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -14791,11 +14511,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G312" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G312" s="2" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -14838,11 +14554,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G313" s="2" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -14971,11 +14683,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G316" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G316" s="2" t="inlineStr"/>
       <c r="H316" s="2" t="inlineStr">
         <is>
           <t>20/28</t>
@@ -15018,11 +14726,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G317" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G317" s="2" t="inlineStr"/>
       <c r="H317" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -15925,11 +15629,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G338" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G338" s="2" t="inlineStr"/>
       <c r="H338" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -15972,11 +15672,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G339" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G339" s="2" t="inlineStr"/>
       <c r="H339" s="2" t="inlineStr">
         <is>
           <t>26/29</t>
@@ -16019,11 +15715,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G340" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G340" s="2" t="inlineStr"/>
       <c r="H340" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -16066,11 +15758,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G341" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G341" s="2" t="inlineStr"/>
       <c r="H341" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -16199,11 +15887,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G344" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G344" s="2" t="inlineStr"/>
       <c r="H344" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -16246,11 +15930,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G345" s="2" t="inlineStr"/>
       <c r="H345" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -17153,11 +16833,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G366" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G366" s="2" t="inlineStr"/>
       <c r="H366" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -17200,11 +16876,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G367" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G367" s="2" t="inlineStr"/>
       <c r="H367" s="2" t="inlineStr">
         <is>
           <t>26/29</t>
@@ -17247,11 +16919,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G368" s="2" t="inlineStr"/>
       <c r="H368" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -17294,11 +16962,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G369" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G369" s="2" t="inlineStr"/>
       <c r="H369" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -17427,11 +17091,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G372" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G372" s="2" t="inlineStr"/>
       <c r="H372" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -17474,11 +17134,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G373" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G373" s="2" t="inlineStr"/>
       <c r="H373" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -18381,11 +18037,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G394" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G394" s="2" t="inlineStr"/>
       <c r="H394" s="2" t="inlineStr">
         <is>
           <t>33/33</t>
@@ -18428,11 +18080,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G395" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G395" s="2" t="inlineStr"/>
       <c r="H395" s="2" t="inlineStr">
         <is>
           <t>31/33</t>
@@ -18475,11 +18123,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G396" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G396" s="2" t="inlineStr"/>
       <c r="H396" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -18522,11 +18166,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G397" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G397" s="2" t="inlineStr"/>
       <c r="H397" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -18655,11 +18295,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G400" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G400" s="2" t="inlineStr"/>
       <c r="H400" s="2" t="inlineStr">
         <is>
           <t>25/33</t>
@@ -18702,11 +18338,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G401" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G401" s="2" t="inlineStr"/>
       <c r="H401" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -19609,11 +19241,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G422" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G422" s="2" t="inlineStr"/>
       <c r="H422" s="2" t="inlineStr">
         <is>
           <t>33/33</t>
@@ -19656,11 +19284,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G423" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G423" s="2" t="inlineStr"/>
       <c r="H423" s="2" t="inlineStr">
         <is>
           <t>31/33</t>
@@ -19703,11 +19327,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -19750,11 +19370,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G425" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G425" s="2" t="inlineStr"/>
       <c r="H425" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -19883,11 +19499,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G428" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G428" s="2" t="inlineStr"/>
       <c r="H428" s="2" t="inlineStr">
         <is>
           <t>25/33</t>
@@ -19930,11 +19542,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G429" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G429" s="2" t="inlineStr"/>
       <c r="H429" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -20837,11 +20445,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G450" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G450" s="2" t="inlineStr"/>
       <c r="H450" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -20884,11 +20488,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G451" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G451" s="2" t="inlineStr"/>
       <c r="H451" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -20931,11 +20531,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G452" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G452" s="2" t="inlineStr"/>
       <c r="H452" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -20978,11 +20574,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G453" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G453" s="2" t="inlineStr"/>
       <c r="H453" s="2" t="inlineStr">
         <is>
           <t>18/30</t>
@@ -21111,11 +20703,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G456" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G456" s="2" t="inlineStr"/>
       <c r="H456" s="2" t="inlineStr">
         <is>
           <t>18/30</t>
@@ -21158,11 +20746,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G457" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G457" s="2" t="inlineStr"/>
       <c r="H457" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -22065,11 +21649,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G478" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -22112,11 +21692,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G479" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G479" s="2" t="inlineStr"/>
       <c r="H479" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -22159,11 +21735,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G480" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G480" s="2" t="inlineStr"/>
       <c r="H480" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -22206,11 +21778,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G481" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G481" s="2" t="inlineStr"/>
       <c r="H481" s="2" t="inlineStr">
         <is>
           <t>18/30</t>
@@ -22339,11 +21907,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G484" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G484" s="2" t="inlineStr"/>
       <c r="H484" s="2" t="inlineStr">
         <is>
           <t>18/30</t>
@@ -22386,11 +21950,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G485" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G485" s="2" t="inlineStr"/>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -23293,11 +22853,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G506" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G506" s="2" t="inlineStr"/>
       <c r="H506" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -23340,11 +22896,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G507" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G507" s="2" t="inlineStr"/>
       <c r="H507" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -23387,11 +22939,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G508" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G508" s="2" t="inlineStr"/>
       <c r="H508" s="2" t="inlineStr">
         <is>
           <t>16/27</t>
@@ -23434,11 +22982,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G509" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G509" s="2" t="inlineStr"/>
       <c r="H509" s="2" t="inlineStr">
         <is>
           <t>5/27</t>
@@ -23567,11 +23111,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G512" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G512" s="2" t="inlineStr"/>
       <c r="H512" s="2" t="inlineStr">
         <is>
           <t>13/27</t>
@@ -23614,11 +23154,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G513" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G513" s="2" t="inlineStr"/>
       <c r="H513" s="2" t="inlineStr">
         <is>
           <t>13/27</t>
@@ -24521,11 +24057,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G534" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G534" s="2" t="inlineStr"/>
       <c r="H534" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -24568,11 +24100,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G535" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G535" s="2" t="inlineStr"/>
       <c r="H535" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -24615,11 +24143,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G536" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G536" s="2" t="inlineStr"/>
       <c r="H536" s="2" t="inlineStr">
         <is>
           <t>16/27</t>
@@ -24662,11 +24186,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G537" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G537" s="2" t="inlineStr"/>
       <c r="H537" s="2" t="inlineStr">
         <is>
           <t>5/27</t>
@@ -24795,11 +24315,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G540" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G540" s="2" t="inlineStr"/>
       <c r="H540" s="2" t="inlineStr">
         <is>
           <t>13/27</t>
@@ -24842,11 +24358,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G541" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G541" s="2" t="inlineStr"/>
       <c r="H541" s="2" t="inlineStr">
         <is>
           <t>13/27</t>
@@ -25749,11 +25261,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G562" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G562" s="2" t="inlineStr"/>
       <c r="H562" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -25796,11 +25304,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G563" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G563" s="2" t="inlineStr"/>
       <c r="H563" s="2" t="inlineStr">
         <is>
           <t>17/29</t>
@@ -25843,11 +25347,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G564" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G564" s="2" t="inlineStr"/>
       <c r="H564" s="2" t="inlineStr">
         <is>
           <t>17/29</t>
@@ -25890,11 +25390,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G565" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G565" s="2" t="inlineStr"/>
       <c r="H565" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -26023,11 +25519,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G568" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G568" s="2" t="inlineStr"/>
       <c r="H568" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -26070,11 +25562,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G569" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G569" s="2" t="inlineStr"/>
       <c r="H569" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -26977,11 +26465,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G590" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -27024,11 +26508,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G591" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G591" s="2" t="inlineStr"/>
       <c r="H591" s="2" t="inlineStr">
         <is>
           <t>17/29</t>
@@ -27071,11 +26551,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G592" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr">
         <is>
           <t>17/29</t>
@@ -27118,11 +26594,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G593" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G593" s="2" t="inlineStr"/>
       <c r="H593" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -27251,11 +26723,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G596" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -27298,11 +26766,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G597" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G597" s="2" t="inlineStr"/>
       <c r="H597" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -28205,11 +27669,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G618" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G618" s="2" t="inlineStr"/>
       <c r="H618" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
@@ -28252,11 +27712,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G619" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G619" s="2" t="inlineStr"/>
       <c r="H619" s="2" t="inlineStr">
         <is>
           <t>12/29</t>
@@ -28299,11 +27755,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G620" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G620" s="2" t="inlineStr"/>
       <c r="H620" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
@@ -28346,11 +27798,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G621" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G621" s="2" t="inlineStr"/>
       <c r="H621" s="2" t="inlineStr">
         <is>
           <t>10/29</t>
@@ -28479,11 +27927,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G624" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G624" s="2" t="inlineStr"/>
       <c r="H624" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -28526,11 +27970,7 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G625" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G625" s="2" t="inlineStr"/>
       <c r="H625" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -29433,11 +28873,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G646" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G646" s="2" t="inlineStr"/>
       <c r="H646" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
@@ -29480,11 +28916,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G647" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G647" s="2" t="inlineStr"/>
       <c r="H647" s="2" t="inlineStr">
         <is>
           <t>12/29</t>
@@ -29527,11 +28959,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G648" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G648" s="2" t="inlineStr"/>
       <c r="H648" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
@@ -29574,11 +29002,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G649" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G649" s="2" t="inlineStr"/>
       <c r="H649" s="2" t="inlineStr">
         <is>
           <t>10/29</t>
@@ -29707,11 +29131,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G652" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G652" s="2" t="inlineStr"/>
       <c r="H652" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -29754,11 +29174,7 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G653" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G653" s="2" t="inlineStr"/>
       <c r="H653" s="2" t="inlineStr">
         <is>
           <t>21/29</t>

--- a/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
+++ b/attendance_reports/Y5_B2526_Surgery_Pop_Quiz_2_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,7 +571,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -619,7 +623,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -672,7 +680,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -723,7 +735,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -876,7 +892,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18/27</t>
@@ -927,7 +947,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2325,7 +2349,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -2383,7 +2411,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -2441,7 +2473,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -2499,7 +2535,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -2643,7 +2683,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>18/27</t>
@@ -2686,7 +2730,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -3589,7 +3637,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3632,7 +3684,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3675,7 +3731,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>17/31</t>
@@ -3718,7 +3778,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>15/31</t>
@@ -3847,7 +3911,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -3890,7 +3958,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>13/31</t>
@@ -4793,7 +4865,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -4836,7 +4912,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -4879,7 +4959,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>17/31</t>
@@ -4922,7 +5006,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>15/31</t>
@@ -5051,7 +5139,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
@@ -5094,7 +5186,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>13/31</t>
@@ -5997,7 +6093,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>7/19</t>
@@ -6040,7 +6140,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>6/19</t>
@@ -6083,7 +6187,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>3/19</t>
@@ -6126,7 +6234,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>7/19</t>
@@ -6255,7 +6367,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>11/19</t>
@@ -6298,7 +6414,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>10/19</t>
@@ -6556,7 +6676,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>1/19</t>
@@ -7201,7 +7325,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>7/19</t>
@@ -7244,7 +7372,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>6/19</t>
@@ -7287,7 +7419,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
           <t>3/19</t>
@@ -7330,7 +7466,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>7/19</t>
@@ -7459,7 +7599,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>11/19</t>
@@ -7502,7 +7646,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>10/19</t>
@@ -7760,7 +7908,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>1/19</t>
@@ -8405,7 +8557,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -8448,7 +8604,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>16/21</t>
@@ -8491,7 +8651,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -8534,7 +8698,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -8663,7 +8831,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
           <t>13/21</t>
@@ -8706,7 +8878,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -9609,7 +9785,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -9652,7 +9832,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
           <t>16/21</t>
@@ -9695,7 +9879,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -9738,7 +9926,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
           <t>14/21</t>
@@ -9867,7 +10059,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
           <t>13/21</t>
@@ -9910,7 +10106,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
           <t>19/21</t>
@@ -10813,7 +11013,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -10856,7 +11060,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -10899,7 +11107,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -10942,7 +11154,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -11071,7 +11287,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
           <t>24/31</t>
@@ -11114,7 +11334,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
           <t>31/31</t>
@@ -12017,7 +12241,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr"/>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
           <t>29/31</t>
@@ -12060,7 +12288,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
           <t>30/31</t>
@@ -12103,7 +12335,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr"/>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -12146,7 +12382,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr"/>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
           <t>28/31</t>
@@ -12275,7 +12515,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr"/>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
           <t>24/31</t>
@@ -12318,7 +12562,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
           <t>31/31</t>
@@ -13221,7 +13469,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr"/>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -13264,7 +13516,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -13307,7 +13563,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -13350,7 +13610,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -13479,7 +13743,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
           <t>20/28</t>
@@ -13522,7 +13790,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr"/>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -14425,7 +14697,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G310" s="2" t="inlineStr"/>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -14468,7 +14744,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -14511,7 +14791,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G312" s="2" t="inlineStr"/>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -14554,7 +14838,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G313" s="2" t="inlineStr"/>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
           <t>27/28</t>
@@ -14683,7 +14971,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G316" s="2" t="inlineStr"/>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
           <t>20/28</t>
@@ -14726,7 +15018,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G317" s="2" t="inlineStr"/>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -15629,7 +15925,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G338" s="2" t="inlineStr"/>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -15672,7 +15972,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G339" s="2" t="inlineStr"/>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
           <t>26/29</t>
@@ -15715,7 +16019,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G340" s="2" t="inlineStr"/>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -15758,7 +16066,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G341" s="2" t="inlineStr"/>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -15887,7 +16199,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G344" s="2" t="inlineStr"/>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -15930,7 +16246,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G345" s="2" t="inlineStr"/>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -16833,7 +17153,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G366" s="2" t="inlineStr"/>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -16876,7 +17200,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G367" s="2" t="inlineStr"/>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
           <t>26/29</t>
@@ -16919,7 +17247,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G368" s="2" t="inlineStr"/>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
           <t>27/29</t>
@@ -16962,7 +17294,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G369" s="2" t="inlineStr"/>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -17091,7 +17427,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G372" s="2" t="inlineStr"/>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
@@ -17134,7 +17474,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G373" s="2" t="inlineStr"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -18037,7 +18381,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G394" s="2" t="inlineStr"/>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
           <t>33/33</t>
@@ -18080,7 +18428,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G395" s="2" t="inlineStr"/>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H395" s="2" t="inlineStr">
         <is>
           <t>31/33</t>
@@ -18123,7 +18475,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G396" s="2" t="inlineStr"/>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H396" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -18166,7 +18522,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G397" s="2" t="inlineStr"/>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H397" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -18295,7 +18655,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G400" s="2" t="inlineStr"/>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
           <t>25/33</t>
@@ -18338,7 +18702,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G401" s="2" t="inlineStr"/>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H401" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -19241,7 +19609,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G422" s="2" t="inlineStr"/>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
           <t>33/33</t>
@@ -19284,7 +19656,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G423" s="2" t="inlineStr"/>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
           <t>31/33</t>
@@ -19327,7 +19703,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G424" s="2" t="inlineStr"/>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -19370,7 +19750,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G425" s="2" t="inlineStr"/>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H425" s="2" t="inlineStr">
         <is>
           <t>28/33</t>
@@ -19499,7 +19883,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G428" s="2" t="inlineStr"/>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
           <t>25/33</t>
@@ -19542,7 +19930,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G429" s="2" t="inlineStr"/>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
           <t>30/33</t>
@@ -20445,7 +20837,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G450" s="2" t="inlineStr"/>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -20488,7 +20884,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G451" s="2" t="inlineStr"/>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -20531,7 +20931,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G452" s="2" t="inlineStr"/>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H452" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -20574,7 +20978,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G453" s="2" t="inlineStr"/>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
           <t>18/30</t>
@@ -20703,7 +21111,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G456" s="2" t="inlineStr"/>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
           <t>18/30</t>
@@ -20746,7 +21158,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G457" s="2" t="inlineStr"/>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -21649,7 +22065,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G478" s="2" t="inlineStr"/>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -21692,7 +22112,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G479" s="2" t="inlineStr"/>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -21735,7 +22159,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G480" s="2" t="inlineStr"/>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -21778,7 +22206,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G481" s="2" t="inlineStr"/>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
           <t>18/30</t>
@@ -21907,7 +22339,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G484" s="2" t="inlineStr"/>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
           <t>18/30</t>
@@ -21950,7 +22386,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G485" s="2" t="inlineStr"/>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -22853,7 +23293,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G506" s="2" t="inlineStr"/>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -22896,7 +23340,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G507" s="2" t="inlineStr"/>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -22939,7 +23387,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G508" s="2" t="inlineStr"/>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
           <t>16/27</t>
@@ -22982,7 +23434,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G509" s="2" t="inlineStr"/>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
           <t>5/27</t>
@@ -23111,7 +23567,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G512" s="2" t="inlineStr"/>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
           <t>13/27</t>
@@ -23154,7 +23614,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G513" s="2" t="inlineStr"/>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
           <t>13/27</t>
@@ -24057,7 +24521,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G534" s="2" t="inlineStr"/>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -24100,7 +24568,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G535" s="2" t="inlineStr"/>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H535" s="2" t="inlineStr">
         <is>
           <t>12/27</t>
@@ -24143,7 +24615,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G536" s="2" t="inlineStr"/>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H536" s="2" t="inlineStr">
         <is>
           <t>16/27</t>
@@ -24186,7 +24662,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G537" s="2" t="inlineStr"/>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
           <t>5/27</t>
@@ -24315,7 +24795,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G540" s="2" t="inlineStr"/>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H540" s="2" t="inlineStr">
         <is>
           <t>13/27</t>
@@ -24358,7 +24842,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G541" s="2" t="inlineStr"/>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H541" s="2" t="inlineStr">
         <is>
           <t>13/27</t>
@@ -25261,7 +25749,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G562" s="2" t="inlineStr"/>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H562" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -25304,7 +25796,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G563" s="2" t="inlineStr"/>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H563" s="2" t="inlineStr">
         <is>
           <t>17/29</t>
@@ -25347,7 +25843,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G564" s="2" t="inlineStr"/>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H564" s="2" t="inlineStr">
         <is>
           <t>17/29</t>
@@ -25390,7 +25890,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G565" s="2" t="inlineStr"/>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H565" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -25519,7 +26023,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G568" s="2" t="inlineStr"/>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H568" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -25562,7 +26070,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G569" s="2" t="inlineStr"/>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H569" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -26465,7 +26977,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G590" s="2" t="inlineStr"/>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H590" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -26508,7 +27024,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G591" s="2" t="inlineStr"/>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H591" s="2" t="inlineStr">
         <is>
           <t>17/29</t>
@@ -26551,7 +27071,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H592" s="2" t="inlineStr">
         <is>
           <t>17/29</t>
@@ -26594,7 +27118,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G593" s="2" t="inlineStr"/>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H593" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -26723,7 +27251,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G596" s="2" t="inlineStr"/>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H596" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
@@ -26766,7 +27298,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G597" s="2" t="inlineStr"/>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H597" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -27669,7 +28205,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G618" s="2" t="inlineStr"/>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H618" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
@@ -27712,7 +28252,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G619" s="2" t="inlineStr"/>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H619" s="2" t="inlineStr">
         <is>
           <t>12/29</t>
@@ -27755,7 +28299,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G620" s="2" t="inlineStr"/>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H620" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
@@ -27798,7 +28346,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G621" s="2" t="inlineStr"/>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H621" s="2" t="inlineStr">
         <is>
           <t>10/29</t>
@@ -27927,7 +28479,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G624" s="2" t="inlineStr"/>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H624" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -27970,7 +28526,11 @@
           <t>08:30:00</t>
         </is>
       </c>
-      <c r="G625" s="2" t="inlineStr"/>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H625" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -28873,7 +29433,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G646" s="2" t="inlineStr"/>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H646" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
@@ -28916,7 +29480,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G647" s="2" t="inlineStr"/>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H647" s="2" t="inlineStr">
         <is>
           <t>12/29</t>
@@ -28959,7 +29527,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G648" s="2" t="inlineStr"/>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H648" s="2" t="inlineStr">
         <is>
           <t>13/29</t>
@@ -29002,7 +29574,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G649" s="2" t="inlineStr"/>
+      <c r="G649" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H649" s="2" t="inlineStr">
         <is>
           <t>10/29</t>
@@ -29131,7 +29707,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G652" s="2" t="inlineStr"/>
+      <c r="G652" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H652" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -29174,7 +29754,11 @@
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="G653" s="2" t="inlineStr"/>
+      <c r="G653" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H653" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
